--- a/MOC Rules Matrix.xlsx
+++ b/MOC Rules Matrix.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="10">
   <si>
     <t>Selected Body MOC</t>
   </si>
@@ -22,13 +22,22 @@
     <t>Auto-Select 'Other' MOC</t>
   </si>
   <si>
+    <t>Auto-Select 'Retainer Ring' MOC</t>
+  </si>
+  <si>
     <t>WCB</t>
   </si>
   <si>
     <t>CF8M</t>
   </si>
   <si>
+    <t>4A</t>
+  </si>
+  <si>
     <t>5A</t>
+  </si>
+  <si>
+    <t>6A</t>
   </si>
   <si>
     <t>C98500</t>
@@ -82,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -92,8 +101,11 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -315,7 +327,7 @@
     <col customWidth="1" min="1" max="1" width="16.25"/>
     <col customWidth="1" min="2" max="2" width="19.75"/>
     <col customWidth="1" min="3" max="3" width="19.88"/>
-    <col customWidth="1" min="4" max="4" width="23.5"/>
+    <col customWidth="1" min="4" max="4" width="25.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -328,55 +340,93 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="3"/>
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/MOC Rules Matrix.xlsx
+++ b/MOC Rules Matrix.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="11">
   <si>
     <t>Selected Body MOC</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t>CF8M</t>
+  </si>
+  <si>
+    <t>CF8M(Dual)</t>
   </si>
   <si>
     <t>4A</t>
@@ -379,24 +382,24 @@
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -407,10 +410,10 @@
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -421,11 +424,25 @@
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/MOC Rules Matrix.xlsx
+++ b/MOC Rules Matrix.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Butterfly" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Ball" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,21 +12,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="27">
+  <si>
+    <t>Selection type</t>
+  </si>
   <si>
     <t>Selected Body MOC</t>
   </si>
   <si>
+    <t>Auto select Stem Housing MOC</t>
+  </si>
+  <si>
+    <t>Auto select Trunnion MOC</t>
+  </si>
+  <si>
+    <t>Auto select Gland Flange MOC</t>
+  </si>
+  <si>
+    <t>Auto select Ball</t>
+  </si>
+  <si>
     <t>Auto-Select Flange MOC</t>
   </si>
   <si>
+    <t>Auto select Seat</t>
+  </si>
+  <si>
+    <t>Casting</t>
+  </si>
+  <si>
+    <t>Body MOC</t>
+  </si>
+  <si>
     <t>Auto-Select 'Other' MOC</t>
   </si>
   <si>
+    <t>Ball MOC</t>
+  </si>
+  <si>
     <t>Auto-Select 'Retainer Ring' MOC</t>
   </si>
   <si>
+    <t>Forging</t>
+  </si>
+  <si>
     <t>WCB</t>
+  </si>
+  <si>
+    <t>Metal seat</t>
+  </si>
+  <si>
+    <t>MS Ball</t>
+  </si>
+  <si>
+    <t>MS Seat</t>
+  </si>
+  <si>
+    <t>Soft Seat</t>
+  </si>
+  <si>
+    <t>SS Ball</t>
+  </si>
+  <si>
+    <t>SS Seat</t>
   </si>
   <si>
     <t>CF8M</t>
@@ -50,10 +99,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -94,20 +148,23 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -119,6 +176,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -334,115 +395,206 @@
   </cols>
   <sheetData>
     <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="15.88"/>
+    <col customWidth="1" min="2" max="2" width="24.5"/>
+    <col customWidth="1" min="3" max="3" width="20.63"/>
+    <col customWidth="1" min="4" max="4" width="24.13"/>
+    <col customWidth="1" min="5" max="5" width="15.0"/>
+    <col customWidth="1" min="6" max="6" width="13.13"/>
+    <col customWidth="1" min="7" max="7" width="21.38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>5</v>
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>6</v>
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>10</v>
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/MOC Rules Matrix.xlsx
+++ b/MOC Rules Matrix.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="36">
   <si>
     <t>Selection type</t>
   </si>
@@ -38,19 +38,25 @@
     <t>Auto select Seat</t>
   </si>
   <si>
+    <t>Auto-Select 'Other' MOC</t>
+  </si>
+  <si>
     <t>Casting</t>
   </si>
   <si>
+    <t>Auto-Select 'Retainer Ring' MOC</t>
+  </si>
+  <si>
     <t>Body MOC</t>
   </si>
   <si>
-    <t>Auto-Select 'Other' MOC</t>
-  </si>
-  <si>
     <t>Ball MOC</t>
   </si>
   <si>
-    <t>Auto-Select 'Retainer Ring' MOC</t>
+    <t>Auto-Select 'Stem' MOC</t>
+  </si>
+  <si>
+    <t>Auto-Select 'Bolting set' MOC</t>
   </si>
   <si>
     <t>Forging</t>
@@ -68,6 +74,9 @@
     <t>MS Seat</t>
   </si>
   <si>
+    <t>F316L</t>
+  </si>
+  <si>
     <t>Soft Seat</t>
   </si>
   <si>
@@ -77,6 +86,9 @@
     <t>SS Seat</t>
   </si>
   <si>
+    <t>B8/8M</t>
+  </si>
+  <si>
     <t>CF8M</t>
   </si>
   <si>
@@ -86,13 +98,28 @@
     <t>4A</t>
   </si>
   <si>
+    <t>F51</t>
+  </si>
+  <si>
     <t>5A</t>
   </si>
   <si>
+    <t>F53</t>
+  </si>
+  <si>
     <t>6A</t>
   </si>
   <si>
+    <t>F55</t>
+  </si>
+  <si>
     <t>C98500</t>
+  </si>
+  <si>
+    <t>MonelK500 / Inconel 718</t>
+  </si>
+  <si>
+    <t>MonelK500</t>
   </si>
 </sst>
 </file>
@@ -148,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -161,11 +188,14 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -391,7 +421,7 @@
     <col customWidth="1" min="1" max="1" width="16.25"/>
     <col customWidth="1" min="2" max="2" width="19.75"/>
     <col customWidth="1" min="3" max="3" width="19.88"/>
-    <col customWidth="1" min="4" max="4" width="25.5"/>
+    <col customWidth="1" min="4" max="6" width="25.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -402,108 +432,156 @@
         <v>6</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>12</v>
+      <c r="E1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
+      <c r="A4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>23</v>
+      <c r="A5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -549,52 +627,52 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
